--- a/CreateAuctionTestData.xlsx
+++ b/CreateAuctionTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\đồ án\Test unit\TestProject1\Realtime-Auction-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B104A72-F10C-420E-A69E-99DEBAF0603F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73A01F7-31EC-4190-8D5D-080F59998521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{65F194C7-9389-4FA5-9B7F-7361B7568721}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="100">
   <si>
     <t>Step_ID</t>
   </si>
@@ -33,30 +33,9 @@
     <t>Scenario_Name</t>
   </si>
   <si>
-    <t>ProductName</t>
-  </si>
-  <si>
-    <t>ImagePath</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>StartPrice</t>
-  </si>
-  <si>
-    <t>PriceStep</t>
-  </si>
-  <si>
     <t>StartTime_Type</t>
   </si>
   <si>
-    <t>StartDate</t>
-  </si>
-  <si>
-    <t>EndDate</t>
-  </si>
-  <si>
     <t>ExpectedMessage</t>
   </si>
   <si>
@@ -81,9 +60,6 @@
     <t>30/05/2026 12:00</t>
   </si>
   <si>
-    <t>Tạo phiên đấu giá thành công!</t>
-  </si>
-  <si>
     <t>Create_Success</t>
   </si>
   <si>
@@ -102,12 +78,6 @@
     <t>SCHEDULE</t>
   </si>
   <si>
-    <t>25/05/2026 08:00</t>
-  </si>
-  <si>
-    <t>30/05/2026 18:00</t>
-  </si>
-  <si>
     <t>A03</t>
   </si>
   <si>
@@ -117,9 +87,6 @@
     <t>Hàng đẹp</t>
   </si>
   <si>
-    <t>Tên sản phẩm không được để trống!</t>
-  </si>
-  <si>
     <t>Check_Inline_Error</t>
   </si>
   <si>
@@ -132,12 +99,6 @@
     <t>A05</t>
   </si>
   <si>
-    <t>Đồng hồ Rolex Submariner chính hãng Thụy Sĩ phiên bản giới hạn đặc biệt dành cho các quý ông thượng lưu 2026</t>
-  </si>
-  <si>
-    <t>Tên sản phẩm không được vượt quá 100 ký tự!</t>
-  </si>
-  <si>
     <t>A06</t>
   </si>
   <si>
@@ -147,12 +108,6 @@
     <t>A07</t>
   </si>
   <si>
-    <t>Mô tả rất dài... (Lặp lại chữ hàng đẹp vượt quá 1000 ký tự)</t>
-  </si>
-  <si>
-    <t>Mô tả không được vượt quá 1000 ký tự!</t>
-  </si>
-  <si>
     <t>A08</t>
   </si>
   <si>
@@ -168,9 +123,6 @@
     <t>Giá khởi điểm nhập số âm</t>
   </si>
   <si>
-    <t>Giá khởi điểm phải lớn hơn hoặc bằng 0!</t>
-  </si>
-  <si>
     <t>A10</t>
   </si>
   <si>
@@ -180,18 +132,12 @@
     <t>abc</t>
   </si>
   <si>
-    <t>Giá khởi điểm phải là số tự nhiên!</t>
-  </si>
-  <si>
     <t>A11</t>
   </si>
   <si>
     <t>Giá khởi điểm là số thập phân</t>
   </si>
   <si>
-    <t>Giá khởi điểm phải là số nguyên!</t>
-  </si>
-  <si>
     <t>A12</t>
   </si>
   <si>
@@ -204,18 +150,12 @@
     <t>Bước giá để trống</t>
   </si>
   <si>
-    <t>Bước giá không được để trống!</t>
-  </si>
-  <si>
     <t>A14</t>
   </si>
   <si>
     <t>Bước giá nhập số âm</t>
   </si>
   <si>
-    <t>Bước giá phải lớn hơn hoặc bằng 0!</t>
-  </si>
-  <si>
     <t>A15</t>
   </si>
   <si>
@@ -225,18 +165,12 @@
     <t>xyz</t>
   </si>
   <si>
-    <t>Bước giá phải là số tự nhiên!</t>
-  </si>
-  <si>
     <t>A16</t>
   </si>
   <si>
     <t>Bước giá nhập số thập phân</t>
   </si>
   <si>
-    <t>Bước giá phải là số nguyên!</t>
-  </si>
-  <si>
     <t>A17</t>
   </si>
   <si>
@@ -261,9 +195,6 @@
     <t>20/05/2025 08:00</t>
   </si>
   <si>
-    <t>Thời gian bắt đầu phải ở trong tương lai!</t>
-  </si>
-  <si>
     <t>A20</t>
   </si>
   <si>
@@ -273,9 +204,6 @@
     <t>31/05/2026 08:00</t>
   </si>
   <si>
-    <t>Thời gian kết thúc phải sau thời gian bắt đầu!</t>
-  </si>
-  <si>
     <t>A21</t>
   </si>
   <si>
@@ -288,9 +216,6 @@
     <t>Lên sàn ngay - Để trống Ngày kết thúc</t>
   </si>
   <si>
-    <t>Vui lòng chọn ngày kết thúc!</t>
-  </si>
-  <si>
     <t>A23</t>
   </si>
   <si>
@@ -300,24 +225,12 @@
     <t>20/05/2025 00:00</t>
   </si>
   <si>
-    <t>Chỉ có thể chọn thời điểm trong tương lai</t>
-  </si>
-  <si>
     <t>A24</t>
   </si>
   <si>
     <t>Ảnh sản phẩm để trống</t>
   </si>
   <si>
-    <t>Vui lòng tải lên ảnh sản phẩm!</t>
-  </si>
-  <si>
-    <t>A25</t>
-  </si>
-  <si>
-    <t>Định dạng file không hợp lệ! (Chỉ nhận JPG, PNG, WEBP)</t>
-  </si>
-  <si>
     <t>Check_Toast_Error</t>
   </si>
   <si>
@@ -336,23 +249,90 @@
     <t>Mô tả chi tiết quá dài (&gt; 200 ký tự)</t>
   </si>
   <si>
-    <t>ảnh hợp lệ.png</t>
-  </si>
-  <si>
-    <t>Ảnh sản phẩm sai định dạng (.jfif)</t>
-  </si>
-  <si>
-    <t>ảnh không hợp lệ.jfif</t>
-  </si>
-  <si>
-    <t>Ảnh 10mb.jpg</t>
+    <t>Tên sản phẩm</t>
+  </si>
+  <si>
+    <t>Ảnh sản phẩm</t>
+  </si>
+  <si>
+    <t>Mô tả chi tiết</t>
+  </si>
+  <si>
+    <t>Giá khởi điểm</t>
+  </si>
+  <si>
+    <t>Bước giá</t>
+  </si>
+  <si>
+    <t>Thời gian bắt đầu</t>
+  </si>
+  <si>
+    <t>Thời gian kết thúc</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập tên sản phẩm</t>
+  </si>
+  <si>
+    <t>Tên sản phẩm không được vượt quá 150 ký tự!</t>
+  </si>
+  <si>
+    <t>Mô tả không được vượt quá 200 ký tự!</t>
+  </si>
+  <si>
+    <t>Giá khởi điểm phải lớn hơn 0!</t>
+  </si>
+  <si>
+    <t>Skip</t>
+  </si>
+  <si>
+    <t>Bước giá phải lớn hơn 0!</t>
+  </si>
+  <si>
+    <t>Thời gian bắt đầu phải trước thời gian kết thúc!</t>
+  </si>
+  <si>
+    <t>Vui lòng chọn ngày kết thúc</t>
+  </si>
+  <si>
+    <t>Ngày kết thúc phải sau thời điểm hiện tại</t>
+  </si>
+  <si>
+    <t>Vui lòng upload ảnh sản phẩm</t>
+  </si>
+  <si>
+    <t>ảnh 10mb.jpg</t>
+  </si>
+  <si>
+    <t>Thành công! Phiên đấu giá đã được đăng lên sàn!</t>
+  </si>
+  <si>
+    <t>ảnh hợp lệ.jpg</t>
+  </si>
+  <si>
+    <t>25/06/2026 08:00</t>
+  </si>
+  <si>
+    <t>30/07/2026 18:00</t>
+  </si>
+  <si>
+    <t>Đồng hồ Rolex Submariner chính hãng Thụy Sĩ phiên bản giới hạn đặc biệt dành cho các quý ông thượng lưu 2026vvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvv</t>
+  </si>
+  <si>
+    <t>Đồng hồ Rolex Submariner chính hãng Thụy Sĩ phiên bản giới hạn đặc biệt dành cho các quý ông thượng lưu 2026vvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvv
+v</t>
+  </si>
+  <si>
+    <t>30/06//2026 12:00</t>
+  </si>
+  <si>
+    <t>30/06/2026 12:00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,6 +356,13 @@
     <font>
       <sz val="13"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -415,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -423,6 +410,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -738,75 +735,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF1EB824-58D2-4724-8D69-31DE1E204955}">
-  <dimension ref="A1:L27"/>
-  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr defaultColWidth="22.44140625" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="23" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="29.6640625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="15.77734375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="21.21875" style="2" customWidth="1"/>
-    <col min="9" max="10" width="15.77734375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="21.6640625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="21.77734375" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="10" width="22.44140625" style="2"/>
+    <col min="11" max="11" width="22.44140625" style="6"/>
+    <col min="12" max="16384" width="22.44140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F2" s="3">
         <v>10000000</v>
@@ -815,34 +804,34 @@
         <v>500000</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>18</v>
+        <v>98</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>103</v>
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3">
         <v>25000000</v>
@@ -851,34 +840,34 @@
         <v>200000</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="67.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
-        <v>103</v>
+      <c r="D4" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3">
         <v>10000000</v>
@@ -887,32 +876,32 @@
         <v>500000</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>30</v>
+        <v>10</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="67.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
-        <v>103</v>
+      <c r="D5" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3">
         <v>10000000</v>
@@ -921,34 +910,34 @@
         <v>500000</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>30</v>
+        <v>10</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="185.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="168.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3">
         <v>10000000</v>
@@ -957,31 +946,31 @@
         <v>500000</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>36</v>
+        <v>99</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3">
@@ -991,34 +980,34 @@
         <v>500000</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="67.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="286.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="F8" s="3">
         <v>10000000</v>
@@ -1027,68 +1016,68 @@
         <v>500000</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>41</v>
+        <v>10</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="67.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3">
         <v>500000</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>44</v>
+        <v>10</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="L9" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="67.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="C10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F10" s="3">
         <v>-100000</v>
@@ -1097,70 +1086,68 @@
         <v>500000</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>47</v>
+        <v>10</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G11" s="3">
         <v>500000</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>31</v>
+        <v>10</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F12" s="3">
         <v>100000.5</v>
@@ -1169,34 +1156,34 @@
         <v>500000</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>54</v>
+        <v>10</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
@@ -1205,68 +1192,68 @@
         <v>500000</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F14" s="3">
         <v>10000000</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>59</v>
+        <v>10</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F15" s="3">
         <v>10000000</v>
@@ -1275,70 +1262,68 @@
         <v>-50000</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>62</v>
+        <v>10</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F16" s="3">
         <v>10000000</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>31</v>
+        <v>10</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F17" s="3">
         <v>10000000</v>
@@ -1347,34 +1332,34 @@
         <v>10000.200000000001</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>69</v>
+        <v>10</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F18" s="3">
         <v>10000000</v>
@@ -1383,34 +1368,34 @@
         <v>0</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F19" s="3">
         <v>10000000</v>
@@ -1419,34 +1404,34 @@
         <v>500000</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>74</v>
+        <v>10</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="67.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F20" s="3">
         <v>10000000</v>
@@ -1455,36 +1440,34 @@
         <v>500000</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="67.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F21" s="3">
         <v>10000000</v>
@@ -1493,36 +1476,36 @@
         <v>500000</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>82</v>
+        <v>10</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="67.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F22" s="3">
         <v>10000000</v>
@@ -1531,36 +1514,36 @@
         <v>500000</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>82</v>
+        <v>10</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F23" s="3">
         <v>10000000</v>
@@ -1569,32 +1552,32 @@
         <v>500000</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="3" t="s">
-        <v>87</v>
+      <c r="K23" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="67.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F24" s="3">
         <v>10000000</v>
@@ -1603,32 +1586,32 @@
         <v>500000</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>91</v>
+        <v>65</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F25" s="3">
         <v>10000000</v>
@@ -1637,34 +1620,34 @@
         <v>500000</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>94</v>
+        <v>10</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F26" s="3">
         <v>10000000</v>
@@ -1673,53 +1656,17 @@
         <v>500000</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>96</v>
+        <v>10</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="67.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F27" s="3">
-        <v>10000000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>500000</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/CreateAuctionTestData.xlsx
+++ b/CreateAuctionTestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\đồ án\Test unit\TestProject1\Realtime-Auction-test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\doantotnghiep\Unit test\Realtime-Auction-Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73A01F7-31EC-4190-8D5D-080F59998521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41B3D32-D92E-45F0-A005-80FE91AE2A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{65F194C7-9389-4FA5-9B7F-7361B7568721}"/>
+    <workbookView xWindow="12" yWindow="12" windowWidth="23016" windowHeight="12936" xr2:uid="{65F194C7-9389-4FA5-9B7F-7361B7568721}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -439,9 +442,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -479,7 +482,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -585,7 +588,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -727,7 +730,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1169,7 +1172,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>37</v>
       </c>
@@ -1199,7 +1202,7 @@
         <v>10</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>11</v>
@@ -1345,7 +1348,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
@@ -1375,7 +1378,7 @@
         <v>10</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>11</v>
